--- a/results/qc/depmap_expression_QC.xlsx
+++ b/results/qc/depmap_expression_QC.xlsx
@@ -10,14 +10,13 @@
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
     <sheet name="Glioma_Cohort" sheetId="2" r:id="rId2"/>
     <sheet name="Missing_Expression" sheetId="3" r:id="rId3"/>
-    <sheet name="Duplicate_Model_IDs" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="213">
   <si>
     <t>Metric</t>
   </si>
@@ -656,159 +655,6 @@
   </si>
   <si>
     <t>CCLF_NEURO_0005_T</t>
-  </si>
-  <si>
-    <t>ACH-001619</t>
-  </si>
-  <si>
-    <t>ACH-001745</t>
-  </si>
-  <si>
-    <t>ACH-000008</t>
-  </si>
-  <si>
-    <t>ACH-000700</t>
-  </si>
-  <si>
-    <t>ACH-002790</t>
-  </si>
-  <si>
-    <t>ACH-001864</t>
-  </si>
-  <si>
-    <t>ACH-000488</t>
-  </si>
-  <si>
-    <t>ACH-000004</t>
-  </si>
-  <si>
-    <t>ACH-002508</t>
-  </si>
-  <si>
-    <t>ACH-000946</t>
-  </si>
-  <si>
-    <t>ACH-000019</t>
-  </si>
-  <si>
-    <t>ACH-000597</t>
-  </si>
-  <si>
-    <t>ACH-001192</t>
-  </si>
-  <si>
-    <t>ACH-002475</t>
-  </si>
-  <si>
-    <t>ACH-000672</t>
-  </si>
-  <si>
-    <t>ACH-002016</t>
-  </si>
-  <si>
-    <t>ACH-001765</t>
-  </si>
-  <si>
-    <t>ACH-000898</t>
-  </si>
-  <si>
-    <t>ACH-000517</t>
-  </si>
-  <si>
-    <t>ACH-000532</t>
-  </si>
-  <si>
-    <t>ACH-001164</t>
-  </si>
-  <si>
-    <t>ACH-000975</t>
-  </si>
-  <si>
-    <t>ACH-000556</t>
-  </si>
-  <si>
-    <t>ACH-001858</t>
-  </si>
-  <si>
-    <t>ACH-000318</t>
-  </si>
-  <si>
-    <t>ACH-001485</t>
-  </si>
-  <si>
-    <t>ACH-000263</t>
-  </si>
-  <si>
-    <t>ACH-002511</t>
-  </si>
-  <si>
-    <t>ACH-000015</t>
-  </si>
-  <si>
-    <t>ACH-003012</t>
-  </si>
-  <si>
-    <t>ACH-000637</t>
-  </si>
-  <si>
-    <t>ACH-000396</t>
-  </si>
-  <si>
-    <t>ACH-000855</t>
-  </si>
-  <si>
-    <t>ACH-002051</t>
-  </si>
-  <si>
-    <t>ACH-000616</t>
-  </si>
-  <si>
-    <t>ACH-001638</t>
-  </si>
-  <si>
-    <t>ACH-000143</t>
-  </si>
-  <si>
-    <t>ACH-000694</t>
-  </si>
-  <si>
-    <t>ACH-000468</t>
-  </si>
-  <si>
-    <t>ACH-002510</t>
-  </si>
-  <si>
-    <t>ACH-001510</t>
-  </si>
-  <si>
-    <t>ACH-001543</t>
-  </si>
-  <si>
-    <t>ACH-000931</t>
-  </si>
-  <si>
-    <t>ACH-000206</t>
-  </si>
-  <si>
-    <t>ACH-000095</t>
-  </si>
-  <si>
-    <t>ACH-000029</t>
-  </si>
-  <si>
-    <t>ACH-001674</t>
-  </si>
-  <si>
-    <t>ACH-000337</t>
-  </si>
-  <si>
-    <t>ACH-000557</t>
-  </si>
-  <si>
-    <t>ACH-000466</t>
-  </si>
-  <si>
-    <t>ACH-003186</t>
   </si>
 </sst>
 </file>
@@ -1220,7 +1066,7 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -2460,289 +2306,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A55"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1">
-      <c r="A2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
-      <c r="A4" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1">
-      <c r="A31" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1">
-      <c r="A34" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1">
-      <c r="A36" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1">
-      <c r="A37" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1">
-      <c r="A40" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1">
-      <c r="A43" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1">
-      <c r="A46" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1">
-      <c r="A50" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1">
-      <c r="A51" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1">
-      <c r="A52" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1">
-      <c r="A53" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1">
-      <c r="A54" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1">
-      <c r="A55" t="s">
-        <v>263</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>